--- a/engine/publish_queue/ARCC/ARCC_Valuation_Model_10092026_public.xlsx
+++ b/engine/publish_queue/ARCC/ARCC_Valuation_Model_10092026_public.xlsx
@@ -76,10 +76,10 @@
       <color rgb="006E7B77"/>
     </font>
     <font>
-      <color rgb="00008000"/>
+      <color rgb="00000000"/>
     </font>
     <font>
-      <color rgb="00000000"/>
+      <color rgb="00008000"/>
     </font>
     <font>
       <b val="1"/>
@@ -134,23 +134,23 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -158,26 +158,26 @@
     <xf numFmtId="167" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="171" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="171" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="172" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="173" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="171" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1332,35 +1332,35 @@
           <t>TOTAL ASSETS</t>
         </is>
       </c>
-      <c r="B11" s="32">
+      <c r="B11" s="33">
         <f>Assumptions!$B$107</f>
         <v/>
       </c>
-      <c r="C11" s="32">
+      <c r="C11" s="33">
         <f>Assumptions!$B$106</f>
         <v/>
       </c>
-      <c r="D11" s="32">
+      <c r="D11" s="33">
         <f>Assumptions!$B$105</f>
         <v/>
       </c>
-      <c r="E11" s="37">
+      <c r="E11" s="38">
         <f>E8+E9+E10</f>
         <v/>
       </c>
-      <c r="F11" s="37">
+      <c r="F11" s="38">
         <f>F8+F9+F10</f>
         <v/>
       </c>
-      <c r="G11" s="37">
+      <c r="G11" s="38">
         <f>G8+G9+G10</f>
         <v/>
       </c>
-      <c r="H11" s="37">
+      <c r="H11" s="38">
         <f>H8+H9+H10</f>
         <v/>
       </c>
-      <c r="I11" s="37">
+      <c r="I11" s="38">
         <f>I8+I9+I10</f>
         <v/>
       </c>
@@ -1472,35 +1472,35 @@
           <t>Equity attributable to owners</t>
         </is>
       </c>
-      <c r="B15" s="32">
+      <c r="B15" s="33">
         <f>Assumptions!$B$120</f>
         <v/>
       </c>
-      <c r="C15" s="32">
+      <c r="C15" s="33">
         <f>Assumptions!$B$119</f>
         <v/>
       </c>
-      <c r="D15" s="32">
+      <c r="D15" s="33">
         <f>Assumptions!$B$118</f>
         <v/>
       </c>
-      <c r="E15" s="37">
+      <c r="E15" s="38">
         <f>D15-Assumptions!$B$134+'Income Statement'!E20-'Income Statement'!E22</f>
         <v/>
       </c>
-      <c r="F15" s="37">
+      <c r="F15" s="38">
         <f>E15+'Income Statement'!F20-'Income Statement'!F22</f>
         <v/>
       </c>
-      <c r="G15" s="37">
+      <c r="G15" s="38">
         <f>F15+'Income Statement'!G20-'Income Statement'!G22</f>
         <v/>
       </c>
-      <c r="H15" s="37">
+      <c r="H15" s="38">
         <f>G15+'Income Statement'!H20-'Income Statement'!H22</f>
         <v/>
       </c>
-      <c r="I15" s="37">
+      <c r="I15" s="38">
         <f>H15+'Income Statement'!I20-'Income Statement'!I22</f>
         <v/>
       </c>
@@ -1892,27 +1892,27 @@
           <t>Cash from operations</t>
         </is>
       </c>
-      <c r="B8" s="37">
+      <c r="B8" s="38">
         <f>B5+B6</f>
         <v/>
       </c>
-      <c r="C8" s="37">
+      <c r="C8" s="38">
         <f>C5+C6+C7</f>
         <v/>
       </c>
-      <c r="D8" s="37">
+      <c r="D8" s="38">
         <f>D5+D6+D7</f>
         <v/>
       </c>
-      <c r="E8" s="37">
+      <c r="E8" s="38">
         <f>E5+E6+E7</f>
         <v/>
       </c>
-      <c r="F8" s="37">
+      <c r="F8" s="38">
         <f>F5+F6+F7</f>
         <v/>
       </c>
-      <c r="G8" s="37">
+      <c r="G8" s="38">
         <f>G5+G6+G7</f>
         <v/>
       </c>
@@ -1954,27 +1954,27 @@
           <t>Free cash flow to equity</t>
         </is>
       </c>
-      <c r="B10" s="37">
+      <c r="B10" s="38">
         <f>B8+B9</f>
         <v/>
       </c>
-      <c r="C10" s="37">
+      <c r="C10" s="38">
         <f>C8+C9</f>
         <v/>
       </c>
-      <c r="D10" s="37">
+      <c r="D10" s="38">
         <f>D8+D9</f>
         <v/>
       </c>
-      <c r="E10" s="37">
+      <c r="E10" s="38">
         <f>E8+E9</f>
         <v/>
       </c>
-      <c r="F10" s="37">
+      <c r="F10" s="38">
         <f>F8+F9</f>
         <v/>
       </c>
-      <c r="G10" s="37">
+      <c r="G10" s="38">
         <f>G8+G9</f>
         <v/>
       </c>
@@ -2808,7 +2808,7 @@
           <t>Windows scored</t>
         </is>
       </c>
-      <c r="B24" s="30" t="n">
+      <c r="B24" s="31" t="n">
         <v>16</v>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
           <t>Cone width against the benchmark</t>
         </is>
       </c>
-      <c r="B28" s="31" t="n">
+      <c r="B28" s="32" t="n">
         <v>1.234292255993717</v>
       </c>
     </row>
@@ -3542,35 +3542,35 @@
           <t>Price / earnings (at spot)</t>
         </is>
       </c>
-      <c r="B7" s="40">
+      <c r="B7" s="41">
         <f>Assumptions!$B$5/B5</f>
         <v/>
       </c>
-      <c r="C7" s="40">
+      <c r="C7" s="41">
         <f>Assumptions!$B$5/C5</f>
         <v/>
       </c>
-      <c r="D7" s="40">
+      <c r="D7" s="41">
         <f>Assumptions!$B$5/D5</f>
         <v/>
       </c>
-      <c r="E7" s="40">
+      <c r="E7" s="41">
         <f>Assumptions!$B$5/E5</f>
         <v/>
       </c>
-      <c r="F7" s="40">
+      <c r="F7" s="41">
         <f>Assumptions!$B$5/F5</f>
         <v/>
       </c>
-      <c r="G7" s="40">
+      <c r="G7" s="41">
         <f>Assumptions!$B$5/G5</f>
         <v/>
       </c>
-      <c r="H7" s="40">
+      <c r="H7" s="41">
         <f>Assumptions!$B$5/H5</f>
         <v/>
       </c>
-      <c r="I7" s="40">
+      <c r="I7" s="41">
         <f>Assumptions!$B$5/I5</f>
         <v/>
       </c>
@@ -3581,35 +3581,35 @@
           <t>Price / book (at spot)</t>
         </is>
       </c>
-      <c r="B8" s="40">
+      <c r="B8" s="41">
         <f>Assumptions!$B$5/B6</f>
         <v/>
       </c>
-      <c r="C8" s="40">
+      <c r="C8" s="41">
         <f>Assumptions!$B$5/C6</f>
         <v/>
       </c>
-      <c r="D8" s="40">
+      <c r="D8" s="41">
         <f>Assumptions!$B$5/D6</f>
         <v/>
       </c>
-      <c r="E8" s="40">
+      <c r="E8" s="41">
         <f>Assumptions!$B$5/E6</f>
         <v/>
       </c>
-      <c r="F8" s="40">
+      <c r="F8" s="41">
         <f>Assumptions!$B$5/F6</f>
         <v/>
       </c>
-      <c r="G8" s="40">
+      <c r="G8" s="41">
         <f>Assumptions!$B$5/G6</f>
         <v/>
       </c>
-      <c r="H8" s="40">
+      <c r="H8" s="41">
         <f>Assumptions!$B$5/H6</f>
         <v/>
       </c>
-      <c r="I8" s="40">
+      <c r="I8" s="41">
         <f>Assumptions!$B$5/I6</f>
         <v/>
       </c>
@@ -3690,35 +3690,35 @@
           <t>Net (cash) / EBITDA</t>
         </is>
       </c>
-      <c r="B11" s="40">
+      <c r="B11" s="41">
         <f>'Balance Sheet'!B16/'Income Statement'!B14</f>
         <v/>
       </c>
-      <c r="C11" s="40">
+      <c r="C11" s="41">
         <f>'Balance Sheet'!C16/'Income Statement'!C14</f>
         <v/>
       </c>
-      <c r="D11" s="40">
+      <c r="D11" s="41">
         <f>'Balance Sheet'!D16/'Income Statement'!D14</f>
         <v/>
       </c>
-      <c r="E11" s="40">
+      <c r="E11" s="41">
         <f>'Balance Sheet'!E16/'Income Statement'!E14</f>
         <v/>
       </c>
-      <c r="F11" s="40">
+      <c r="F11" s="41">
         <f>'Balance Sheet'!F16/'Income Statement'!F14</f>
         <v/>
       </c>
-      <c r="G11" s="40">
+      <c r="G11" s="41">
         <f>'Balance Sheet'!G16/'Income Statement'!G14</f>
         <v/>
       </c>
-      <c r="H11" s="40">
+      <c r="H11" s="41">
         <f>'Balance Sheet'!H16/'Income Statement'!H14</f>
         <v/>
       </c>
-      <c r="I11" s="40">
+      <c r="I11" s="41">
         <f>'Balance Sheet'!I16/'Income Statement'!I14</f>
         <v/>
       </c>
@@ -4041,11 +4041,11 @@
         <f>DCF!C45</f>
         <v/>
       </c>
-      <c r="E5" s="40">
+      <c r="E5" s="41">
         <f>D5/C5</f>
         <v/>
       </c>
-      <c r="F5" s="40">
+      <c r="F5" s="41">
         <f>D5/B5</f>
         <v/>
       </c>
@@ -4072,11 +4072,11 @@
         <f>Assumptions!$B$171</f>
         <v/>
       </c>
-      <c r="E6" s="40">
+      <c r="E6" s="41">
         <f>D6/C6</f>
         <v/>
       </c>
-      <c r="F6" s="40">
+      <c r="F6" s="41">
         <f>D6/B6</f>
         <v/>
       </c>
@@ -4103,11 +4103,11 @@
         <f>Assumptions!$B$174</f>
         <v/>
       </c>
-      <c r="E7" s="40">
+      <c r="E7" s="41">
         <f>D7/C7</f>
         <v/>
       </c>
-      <c r="F7" s="40">
+      <c r="F7" s="41">
         <f>D7/B7</f>
         <v/>
       </c>
@@ -6070,14 +6070,15 @@
           <t>Equity risk premium, TOTAL (split into the two legs below)</t>
         </is>
       </c>
-      <c r="B43" s="25" t="n">
-        <v>0.0941</v>
+      <c r="B43" s="30">
+        <f>B44+B45</f>
+        <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">   of which the MATURE premium — beta applies to this leg only</t>
+          <t>Mature equity risk premium — beta applies to THIS leg and to nothing else</t>
         </is>
       </c>
       <c r="B44" s="25" t="n">
@@ -6205,7 +6206,7 @@
           <t>FY2023 sales (net)</t>
         </is>
       </c>
-      <c r="B56" s="30" t="n">
+      <c r="B56" s="31" t="n">
         <v>6042.831338</v>
       </c>
     </row>
@@ -6215,7 +6216,7 @@
           <t>FY2024 sales (net)</t>
         </is>
       </c>
-      <c r="B57" s="30" t="n">
+      <c r="B57" s="31" t="n">
         <v>8729.782821000001</v>
       </c>
     </row>
@@ -6225,7 +6226,7 @@
           <t>FY2025 sales (net)</t>
         </is>
       </c>
-      <c r="B58" s="30" t="n">
+      <c r="B58" s="31" t="n">
         <v>12447.320081</v>
       </c>
     </row>
@@ -6235,7 +6236,7 @@
           <t>FY2023 cost of sales</t>
         </is>
       </c>
-      <c r="B59" s="30" t="n">
+      <c r="B59" s="31" t="n">
         <v>4759.815212</v>
       </c>
     </row>
@@ -6245,7 +6246,7 @@
           <t>FY2024 cost of sales</t>
         </is>
       </c>
-      <c r="B60" s="30" t="n">
+      <c r="B60" s="31" t="n">
         <v>6642.972487</v>
       </c>
     </row>
@@ -6255,7 +6256,7 @@
           <t>FY2025 cost of sales</t>
         </is>
       </c>
-      <c r="B61" s="30" t="n">
+      <c r="B61" s="31" t="n">
         <v>7389.054416</v>
       </c>
     </row>
@@ -6265,7 +6266,7 @@
           <t>FY2023 general and administrative expenses</t>
         </is>
       </c>
-      <c r="B62" s="30" t="n">
+      <c r="B62" s="31" t="n">
         <v>183.940276</v>
       </c>
     </row>
@@ -6275,7 +6276,7 @@
           <t>FY2024 general and administrative expenses</t>
         </is>
       </c>
-      <c r="B63" s="30" t="n">
+      <c r="B63" s="31" t="n">
         <v>267.798104</v>
       </c>
     </row>
@@ -6285,7 +6286,7 @@
           <t>FY2025 general and administrative expenses</t>
         </is>
       </c>
-      <c r="B64" s="30" t="n">
+      <c r="B64" s="31" t="n">
         <v>384.332833</v>
       </c>
     </row>
@@ -6295,7 +6296,7 @@
           <t>FY2023 provisions charged</t>
         </is>
       </c>
-      <c r="B65" s="30" t="n">
+      <c r="B65" s="31" t="n">
         <v>15.220195</v>
       </c>
     </row>
@@ -6305,7 +6306,7 @@
           <t>FY2024 provisions charged</t>
         </is>
       </c>
-      <c r="B66" s="30" t="n">
+      <c r="B66" s="31" t="n">
         <v>56.05295</v>
       </c>
     </row>
@@ -6315,7 +6316,7 @@
           <t>FY2025 provisions charged</t>
         </is>
       </c>
-      <c r="B67" s="30" t="n">
+      <c r="B67" s="31" t="n">
         <v>74.505707</v>
       </c>
     </row>
@@ -6325,7 +6326,7 @@
           <t>FY2023 expected credit losses</t>
         </is>
       </c>
-      <c r="B68" s="30" t="n">
+      <c r="B68" s="31" t="n">
         <v>4.745753</v>
       </c>
     </row>
@@ -6335,7 +6336,7 @@
           <t>FY2024 expected credit losses</t>
         </is>
       </c>
-      <c r="B69" s="30" t="n">
+      <c r="B69" s="31" t="n">
         <v>-1.106452</v>
       </c>
     </row>
@@ -6345,7 +6346,7 @@
           <t>FY2025 expected credit losses</t>
         </is>
       </c>
-      <c r="B70" s="30" t="n">
+      <c r="B70" s="31" t="n">
         <v>3.603563</v>
       </c>
     </row>
@@ -6355,7 +6356,7 @@
           <t>FY2023 profit before tax</t>
         </is>
       </c>
-      <c r="B71" s="30" t="n">
+      <c r="B71" s="31" t="n">
         <v>930.231432</v>
       </c>
     </row>
@@ -6365,7 +6366,7 @@
           <t>FY2024 profit before tax</t>
         </is>
       </c>
-      <c r="B72" s="30" t="n">
+      <c r="B72" s="31" t="n">
         <v>1505.866118</v>
       </c>
     </row>
@@ -6375,7 +6376,7 @@
           <t>FY2025 profit before tax</t>
         </is>
       </c>
-      <c r="B73" s="30" t="n">
+      <c r="B73" s="31" t="n">
         <v>4725.157878</v>
       </c>
     </row>
@@ -6385,7 +6386,7 @@
           <t>FY2023 income tax</t>
         </is>
       </c>
-      <c r="B74" s="30" t="n">
+      <c r="B74" s="31" t="n">
         <v>232.732802</v>
       </c>
     </row>
@@ -6395,7 +6396,7 @@
           <t>FY2024 income tax</t>
         </is>
       </c>
-      <c r="B75" s="30" t="n">
+      <c r="B75" s="31" t="n">
         <v>345.730996</v>
       </c>
     </row>
@@ -6405,7 +6406,7 @@
           <t>FY2025 income tax</t>
         </is>
       </c>
-      <c r="B76" s="30" t="n">
+      <c r="B76" s="31" t="n">
         <v>1125.467657</v>
       </c>
     </row>
@@ -6415,7 +6416,7 @@
           <t>FY2023 attributable profit</t>
         </is>
       </c>
-      <c r="B77" s="30" t="n">
+      <c r="B77" s="31" t="n">
         <v>697.488741</v>
       </c>
     </row>
@@ -6425,7 +6426,7 @@
           <t>FY2024 attributable profit</t>
         </is>
       </c>
-      <c r="B78" s="30" t="n">
+      <c r="B78" s="31" t="n">
         <v>1160.129411</v>
       </c>
     </row>
@@ -6435,7 +6436,7 @@
           <t>FY2025 attributable profit</t>
         </is>
       </c>
-      <c r="B79" s="30" t="n">
+      <c r="B79" s="31" t="n">
         <v>3599.585937</v>
       </c>
     </row>
@@ -6490,7 +6491,7 @@
           <t>FY2023 depreciation and amortisation</t>
         </is>
       </c>
-      <c r="B83" s="30" t="n">
+      <c r="B83" s="31" t="n">
         <v>250.424521</v>
       </c>
     </row>
@@ -6500,7 +6501,7 @@
           <t>FY2024 depreciation and amortisation</t>
         </is>
       </c>
-      <c r="B84" s="30" t="n">
+      <c r="B84" s="31" t="n">
         <v>256.801527</v>
       </c>
     </row>
@@ -6510,7 +6511,7 @@
           <t>FY2025 depreciation and amortisation</t>
         </is>
       </c>
-      <c r="B85" s="30" t="n">
+      <c r="B85" s="31" t="n">
         <v>289.771295</v>
       </c>
     </row>
@@ -6520,7 +6521,7 @@
           <t>FY2023 capital expenditure</t>
         </is>
       </c>
-      <c r="B86" s="30" t="n">
+      <c r="B86" s="31" t="n">
         <v>58.543963</v>
       </c>
     </row>
@@ -6530,7 +6531,7 @@
           <t>FY2024 capital expenditure</t>
         </is>
       </c>
-      <c r="B87" s="30" t="n">
+      <c r="B87" s="31" t="n">
         <v>912.0154</v>
       </c>
     </row>
@@ -6540,7 +6541,7 @@
           <t>FY2025 capital expenditure</t>
         </is>
       </c>
-      <c r="B88" s="30" t="n">
+      <c r="B88" s="31" t="n">
         <v>796.47076</v>
       </c>
     </row>
@@ -6550,7 +6551,7 @@
           <t>FY2025 interest income</t>
         </is>
       </c>
-      <c r="B89" s="30" t="n">
+      <c r="B89" s="31" t="n">
         <v>226.274781</v>
       </c>
     </row>
@@ -6560,7 +6561,7 @@
           <t>FY2025 other income</t>
         </is>
       </c>
-      <c r="B90" s="30" t="n">
+      <c r="B90" s="31" t="n">
         <v>53.339508</v>
       </c>
     </row>
@@ -6570,7 +6571,7 @@
           <t>FY2025 finance costs</t>
         </is>
       </c>
-      <c r="B91" s="30" t="n">
+      <c r="B91" s="31" t="n">
         <v>49.841733</v>
       </c>
     </row>
@@ -6580,7 +6581,7 @@
           <t>FY2025 foreign exchange differences</t>
         </is>
       </c>
-      <c r="B92" s="30" t="n">
+      <c r="B92" s="31" t="n">
         <v>-101.57824</v>
       </c>
     </row>
@@ -6605,7 +6606,7 @@
           <t>FY2025 local sales of goods</t>
         </is>
       </c>
-      <c r="B94" s="30" t="n">
+      <c r="B94" s="31" t="n">
         <v>8350.454610000001</v>
       </c>
     </row>
@@ -6615,7 +6616,7 @@
           <t>FY2025 local services</t>
         </is>
       </c>
-      <c r="B95" s="30" t="n">
+      <c r="B95" s="31" t="n">
         <v>281.863546</v>
       </c>
     </row>
@@ -6625,7 +6626,7 @@
           <t>FY2025 export sales of goods</t>
         </is>
       </c>
-      <c r="B96" s="30" t="n">
+      <c r="B96" s="31" t="n">
         <v>3356.422381</v>
       </c>
     </row>
@@ -6635,7 +6636,7 @@
           <t>FY2025 export services</t>
         </is>
       </c>
-      <c r="B97" s="30" t="n">
+      <c r="B97" s="31" t="n">
         <v>458.579544</v>
       </c>
     </row>
@@ -6645,7 +6646,7 @@
           <t>FY2024 total local sales</t>
         </is>
       </c>
-      <c r="B98" s="30" t="n">
+      <c r="B98" s="31" t="n">
         <v>4883.304477</v>
       </c>
     </row>
@@ -6655,7 +6656,7 @@
           <t>FY2024 total export sales</t>
         </is>
       </c>
-      <c r="B99" s="30" t="n">
+      <c r="B99" s="31" t="n">
         <v>3846.478344</v>
       </c>
     </row>
@@ -6665,7 +6666,7 @@
           <t>FY2025 cost of sales — materials and fuel</t>
         </is>
       </c>
-      <c r="B100" s="30" t="n">
+      <c r="B100" s="31" t="n">
         <v>5698.184715</v>
       </c>
     </row>
@@ -6675,7 +6676,7 @@
           <t>FY2025 cost of sales — transportation</t>
         </is>
       </c>
-      <c r="B101" s="30" t="n">
+      <c r="B101" s="31" t="n">
         <v>764.279332</v>
       </c>
     </row>
@@ -6685,7 +6686,7 @@
           <t>FY2025 cost of sales — overheads</t>
         </is>
       </c>
-      <c r="B102" s="30" t="n">
+      <c r="B102" s="31" t="n">
         <v>641.143208</v>
       </c>
     </row>
@@ -6695,7 +6696,7 @@
           <t>FY2025 administrative depreciation</t>
         </is>
       </c>
-      <c r="B103" s="30" t="n">
+      <c r="B103" s="31" t="n">
         <v>4.324134</v>
       </c>
     </row>
@@ -6720,7 +6721,7 @@
           <t>Total assets FY2025</t>
         </is>
       </c>
-      <c r="B105" s="30" t="n">
+      <c r="B105" s="31" t="n">
         <v>8783.721849</v>
       </c>
     </row>
@@ -6730,7 +6731,7 @@
           <t>Total assets FY2024</t>
         </is>
       </c>
-      <c r="B106" s="30" t="n">
+      <c r="B106" s="31" t="n">
         <v>5848.616103</v>
       </c>
     </row>
@@ -6740,7 +6741,7 @@
           <t>Total assets FY2023</t>
         </is>
       </c>
-      <c r="B107" s="30" t="n">
+      <c r="B107" s="31" t="n">
         <v>3887.527427</v>
       </c>
     </row>
@@ -6750,7 +6751,7 @@
           <t>Total liabilities FY2025</t>
         </is>
       </c>
-      <c r="B108" s="30" t="n">
+      <c r="B108" s="31" t="n">
         <v>4140.989609</v>
       </c>
     </row>
@@ -6760,7 +6761,7 @@
           <t>Property, plant and equipment FY2025</t>
         </is>
       </c>
-      <c r="B109" s="30" t="n">
+      <c r="B109" s="31" t="n">
         <v>2522.323523</v>
       </c>
     </row>
@@ -6770,7 +6771,7 @@
           <t>Assets under construction FY2025</t>
         </is>
       </c>
-      <c r="B110" s="30" t="n">
+      <c r="B110" s="31" t="n">
         <v>391.543753</v>
       </c>
     </row>
@@ -6780,7 +6781,7 @@
           <t>Intangible assets FY2025</t>
         </is>
       </c>
-      <c r="B111" s="30" t="n">
+      <c r="B111" s="31" t="n">
         <v>106.799617</v>
       </c>
     </row>
@@ -6790,7 +6791,7 @@
           <t>Inventories FY2025</t>
         </is>
       </c>
-      <c r="B112" s="30" t="n">
+      <c r="B112" s="31" t="n">
         <v>1053.646218</v>
       </c>
     </row>
@@ -6800,7 +6801,7 @@
           <t>Trade receivables FY2025</t>
         </is>
       </c>
-      <c r="B113" s="30" t="n">
+      <c r="B113" s="31" t="n">
         <v>244.416417</v>
       </c>
     </row>
@@ -6810,7 +6811,7 @@
           <t>Debtors and other debit balances FY2025</t>
         </is>
       </c>
-      <c r="B114" s="30" t="n">
+      <c r="B114" s="31" t="n">
         <v>1004.779062</v>
       </c>
     </row>
@@ -6820,7 +6821,7 @@
           <t>Cash and bank balances FY2025</t>
         </is>
       </c>
-      <c r="B115" s="30" t="n">
+      <c r="B115" s="31" t="n">
         <v>3459.391229</v>
       </c>
     </row>
@@ -6830,7 +6831,7 @@
           <t>Cash and bank balances FY2024</t>
         </is>
       </c>
-      <c r="B116" s="30" t="n">
+      <c r="B116" s="31" t="n">
         <v>1687.062873</v>
       </c>
     </row>
@@ -6840,7 +6841,7 @@
           <t>Cash and bank balances FY2023</t>
         </is>
       </c>
-      <c r="B117" s="30" t="n">
+      <c r="B117" s="31" t="n">
         <v>561.09968</v>
       </c>
     </row>
@@ -6850,7 +6851,7 @@
           <t>Equity attributable to owners FY2025</t>
         </is>
       </c>
-      <c r="B118" s="30" t="n">
+      <c r="B118" s="31" t="n">
         <v>4642.574235</v>
       </c>
     </row>
@@ -6860,7 +6861,7 @@
           <t>Equity attributable to owners FY2024</t>
         </is>
       </c>
-      <c r="B119" s="30" t="n">
+      <c r="B119" s="31" t="n">
         <v>2303.472299</v>
       </c>
     </row>
@@ -6870,7 +6871,7 @@
           <t>Equity attributable to owners FY2023</t>
         </is>
       </c>
-      <c r="B120" s="30" t="n">
+      <c r="B120" s="31" t="n">
         <v>1754.221659</v>
       </c>
     </row>
@@ -6905,7 +6906,7 @@
           <t>CIB credit facilities — EGP</t>
         </is>
       </c>
-      <c r="B123" s="30" t="n">
+      <c r="B123" s="31" t="n">
         <v>99.916937</v>
       </c>
     </row>
@@ -6915,7 +6916,7 @@
           <t>National Bank of Egypt facility — EUR</t>
         </is>
       </c>
-      <c r="B124" s="30" t="n">
+      <c r="B124" s="31" t="n">
         <v>145.741484</v>
       </c>
     </row>
@@ -6925,7 +6926,7 @@
           <t>EBRD facility — EUR</t>
         </is>
       </c>
-      <c r="B125" s="30" t="n">
+      <c r="B125" s="31" t="n">
         <v>888.274195</v>
       </c>
     </row>
@@ -6935,7 +6936,7 @@
           <t>Lease liabilities</t>
         </is>
       </c>
-      <c r="B126" s="30" t="n">
+      <c r="B126" s="31" t="n">
         <v>1.176042</v>
       </c>
     </row>
@@ -6945,7 +6946,7 @@
           <t>Total interest-bearing debt FY2024</t>
         </is>
       </c>
-      <c r="B127" s="30" t="n">
+      <c r="B127" s="31" t="n">
         <v>760.917684</v>
       </c>
     </row>
@@ -6955,7 +6956,7 @@
           <t>Total interest-bearing debt FY2023</t>
         </is>
       </c>
-      <c r="B128" s="30" t="n">
+      <c r="B128" s="31" t="n">
         <v>90.07427300000001</v>
       </c>
     </row>
@@ -6965,7 +6966,7 @@
           <t>FY2025 loan interest expense</t>
         </is>
       </c>
-      <c r="B129" s="30" t="n">
+      <c r="B129" s="31" t="n">
         <v>24.61313</v>
       </c>
     </row>
@@ -6975,7 +6976,7 @@
           <t>FY2025 credit-facility interest expense</t>
         </is>
       </c>
-      <c r="B130" s="30" t="n">
+      <c r="B130" s="31" t="n">
         <v>23.00737</v>
       </c>
     </row>
@@ -6985,7 +6986,7 @@
           <t>FY2024 loan interest expense</t>
         </is>
       </c>
-      <c r="B131" s="30" t="n">
+      <c r="B131" s="31" t="n">
         <v>2.754107</v>
       </c>
     </row>
@@ -6995,7 +6996,7 @@
           <t>FY2024 credit-facility interest expense</t>
         </is>
       </c>
-      <c r="B132" s="30" t="n">
+      <c r="B132" s="31" t="n">
         <v>85.95302599999999</v>
       </c>
     </row>
@@ -7020,7 +7021,7 @@
           <t>FY2025 dividend declared</t>
         </is>
       </c>
-      <c r="B134" s="30" t="n">
+      <c r="B134" s="31" t="n">
         <v>2001.79216</v>
       </c>
     </row>
@@ -7030,7 +7031,7 @@
           <t>FY2024 dividend approved and paid</t>
         </is>
       </c>
-      <c r="B135" s="30" t="n">
+      <c r="B135" s="31" t="n">
         <v>1102.110289</v>
       </c>
     </row>
@@ -7040,7 +7041,7 @@
           <t>Q1-2026 sales</t>
         </is>
       </c>
-      <c r="B136" s="30" t="n">
+      <c r="B136" s="31" t="n">
         <v>2995.95935</v>
       </c>
     </row>
@@ -7050,7 +7051,7 @@
           <t>Q1-2025 sales</t>
         </is>
       </c>
-      <c r="B137" s="30" t="n">
+      <c r="B137" s="31" t="n">
         <v>2554.448091</v>
       </c>
     </row>
@@ -7060,7 +7061,7 @@
           <t>Q1-2026 gross profit</t>
         </is>
       </c>
-      <c r="B138" s="30" t="n">
+      <c r="B138" s="31" t="n">
         <v>1286.145881</v>
       </c>
     </row>
@@ -7070,7 +7071,7 @@
           <t>Q1-2026 attributable profit</t>
         </is>
       </c>
-      <c r="B139" s="30" t="n">
+      <c r="B139" s="31" t="n">
         <v>943.068309</v>
       </c>
     </row>
@@ -7080,7 +7081,7 @@
           <t>Q1-2026 cash and bank balances</t>
         </is>
       </c>
-      <c r="B140" s="30" t="n">
+      <c r="B140" s="31" t="n">
         <v>4379.627379</v>
       </c>
     </row>
@@ -7090,7 +7091,7 @@
           <t>Q1-2026 interest-bearing debt</t>
         </is>
       </c>
-      <c r="B141" s="30" t="n">
+      <c r="B141" s="31" t="n">
         <v>1260.509089</v>
       </c>
     </row>
@@ -7100,7 +7101,7 @@
           <t>Cash and bank balances, reviewed 30 June 2026</t>
         </is>
       </c>
-      <c r="B142" s="30" t="n">
+      <c r="B142" s="31" t="n">
         <v>1970.50114</v>
       </c>
     </row>
@@ -7110,7 +7111,7 @@
           <t>Interest-bearing debt, reviewed 30 June 2026</t>
         </is>
       </c>
-      <c r="B143" s="30" t="n">
+      <c r="B143" s="31" t="n">
         <v>1283.288394</v>
       </c>
     </row>
@@ -7200,7 +7201,7 @@
           <t>Q1-2026 dividends payable</t>
         </is>
       </c>
-      <c r="B152" s="30" t="n">
+      <c r="B152" s="31" t="n">
         <v>2001.79216</v>
       </c>
     </row>
@@ -7210,7 +7211,7 @@
           <t>Q1-2026 finance costs</t>
         </is>
       </c>
-      <c r="B153" s="30" t="n">
+      <c r="B153" s="31" t="n">
         <v>11.168843</v>
       </c>
     </row>
@@ -7235,7 +7236,7 @@
           <t>Replacement cost per annual tonne</t>
         </is>
       </c>
-      <c r="B155" s="30" t="n">
+      <c r="B155" s="31" t="n">
         <v>130</v>
       </c>
       <c r="C155" s="5" t="inlineStr">
@@ -7250,7 +7251,7 @@
           <t>Justified enterprise value per annual tonne</t>
         </is>
       </c>
-      <c r="B156" s="30" t="n">
+      <c r="B156" s="31" t="n">
         <v>95</v>
       </c>
       <c r="C156" s="5" t="inlineStr">
@@ -7265,7 +7266,7 @@
           <t>Justified EV/EBITDA</t>
         </is>
       </c>
-      <c r="B157" s="31" t="n">
+      <c r="B157" s="32" t="n">
         <v>4.5</v>
       </c>
     </row>
@@ -7275,7 +7276,7 @@
           <t>Justified price/earnings</t>
         </is>
       </c>
-      <c r="B158" s="31" t="n">
+      <c r="B158" s="32" t="n">
         <v>7</v>
       </c>
     </row>
@@ -7425,7 +7426,7 @@
           <t>Peer — Sinai Cement revenue</t>
         </is>
       </c>
-      <c r="B169" s="30" t="n">
+      <c r="B169" s="31" t="n">
         <v>9090</v>
       </c>
     </row>
@@ -7435,7 +7436,7 @@
           <t>Peer — Sinai Cement profit</t>
         </is>
       </c>
-      <c r="B170" s="30" t="n">
+      <c r="B170" s="31" t="n">
         <v>2290</v>
       </c>
     </row>
@@ -7445,7 +7446,7 @@
           <t>Peer — Sinai Cement market capitalisation</t>
         </is>
       </c>
-      <c r="B171" s="30" t="n">
+      <c r="B171" s="31" t="n">
         <v>20604.19</v>
       </c>
     </row>
@@ -7455,7 +7456,7 @@
           <t>Peer — Misr Beni Suef revenue</t>
         </is>
       </c>
-      <c r="B172" s="30" t="n">
+      <c r="B172" s="31" t="n">
         <v>5700</v>
       </c>
     </row>
@@ -7465,7 +7466,7 @@
           <t>Peer — Misr Beni Suef profit</t>
         </is>
       </c>
-      <c r="B173" s="30" t="n">
+      <c r="B173" s="31" t="n">
         <v>3946</v>
       </c>
     </row>
@@ -7475,7 +7476,7 @@
           <t>Peer — Misr Beni Suef market capitalisation</t>
         </is>
       </c>
-      <c r="B174" s="30" t="n">
+      <c r="B174" s="31" t="n">
         <v>13730</v>
       </c>
     </row>
@@ -7580,7 +7581,7 @@
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="B7" s="32">
+      <c r="B7" s="33">
         <f>DCF!B33</f>
         <v/>
       </c>
@@ -7625,7 +7626,7 @@
           <t>Equity value</t>
         </is>
       </c>
-      <c r="B10" s="32">
+      <c r="B10" s="33">
         <f>DCF!B42</f>
         <v/>
       </c>
@@ -7786,7 +7787,7 @@
           <t>Kiln clinker capacity (Mt, audited note 1)</t>
         </is>
       </c>
-      <c r="B5" s="33">
+      <c r="B5" s="34">
         <f>Assumptions!$B$15</f>
         <v/>
       </c>
@@ -7808,7 +7809,7 @@
           <t>Clinker produced (Mt)</t>
         </is>
       </c>
-      <c r="B7" s="34">
+      <c r="B7" s="35">
         <f>B5*B6</f>
         <v/>
       </c>
@@ -7830,7 +7831,7 @@
           <t>Clinker EXPORTED (Mt)</t>
         </is>
       </c>
-      <c r="B9" s="34">
+      <c r="B9" s="35">
         <f>B7*B8</f>
         <v/>
       </c>
@@ -7841,7 +7842,7 @@
           <t>Clinker ground into cement (Mt)</t>
         </is>
       </c>
-      <c r="B10" s="34">
+      <c r="B10" s="35">
         <f>B7-B9</f>
         <v/>
       </c>
@@ -7852,7 +7853,7 @@
           <t>Clinker factor (t clinker / t cement)</t>
         </is>
       </c>
-      <c r="B11" s="35">
+      <c r="B11" s="36">
         <f>Assumptions!$B$16</f>
         <v/>
       </c>
@@ -7863,7 +7864,7 @@
           <t>Cement produced (Mt)</t>
         </is>
       </c>
-      <c r="B12" s="36">
+      <c r="B12" s="37">
         <f>B10/B11</f>
         <v/>
       </c>
@@ -7874,7 +7875,7 @@
           <t>Cement mill capacity (Mt, audited note 1)</t>
         </is>
       </c>
-      <c r="B13" s="33">
+      <c r="B13" s="34">
         <f>Assumptions!$B$14</f>
         <v/>
       </c>
@@ -7907,7 +7908,7 @@
           <t>Cement EXPORTED (Mt)</t>
         </is>
       </c>
-      <c r="B16" s="34">
+      <c r="B16" s="35">
         <f>B29*B15</f>
         <v/>
       </c>
@@ -7918,7 +7919,7 @@
           <t>Cement sold LOCALLY (Mt)</t>
         </is>
       </c>
-      <c r="B17" s="34">
+      <c r="B17" s="35">
         <f>B29-B16</f>
         <v/>
       </c>
@@ -7929,7 +7930,7 @@
           <t>TOTAL DESPATCHES FY2025 (Mt)</t>
         </is>
       </c>
-      <c r="B18" s="36">
+      <c r="B18" s="37">
         <f>B29+B9</f>
         <v/>
       </c>
@@ -7940,7 +7941,7 @@
           <t>Plus draw from finished-goods stock (Mt)</t>
         </is>
       </c>
-      <c r="B19" s="35">
+      <c r="B19" s="36">
         <f>Assumptions!$B$26</f>
         <v/>
       </c>
@@ -7978,7 +7979,7 @@
           <t>LOCAL CEMENT PRICE (EGP/t) — DERIVED</t>
         </is>
       </c>
-      <c r="B22" s="37">
+      <c r="B22" s="38">
         <f>B21/B17</f>
         <v/>
       </c>
@@ -8000,7 +8001,7 @@
           <t>Clinker price as a fraction of cement</t>
         </is>
       </c>
-      <c r="B24" s="34">
+      <c r="B24" s="35">
         <f>Assumptions!$B$18</f>
         <v/>
       </c>
@@ -8011,7 +8012,7 @@
           <t>Export cement-equivalent tonnes</t>
         </is>
       </c>
-      <c r="B25" s="34">
+      <c r="B25" s="35">
         <f>B16+B9*B24</f>
         <v/>
       </c>
@@ -8022,7 +8023,7 @@
           <t>EXPORT CEMENT PRICE (USD/t) — DERIVED</t>
         </is>
       </c>
-      <c r="B26" s="38">
+      <c r="B26" s="39">
         <f>B23/B25/Assumptions!$B$19</f>
         <v/>
       </c>
@@ -8033,7 +8034,7 @@
           <t>EXPORT CLINKER PRICE (USD/t) — DERIVED</t>
         </is>
       </c>
-      <c r="B27" s="38">
+      <c r="B27" s="39">
         <f>B26*B24</f>
         <v/>
       </c>
@@ -8055,7 +8056,7 @@
           <t>Cement SOLD (Mt)</t>
         </is>
       </c>
-      <c r="B29" s="34">
+      <c r="B29" s="35">
         <f>B12+B19</f>
         <v/>
       </c>
@@ -8159,7 +8160,7 @@
           <t>TOTAL CASH COST PER TONNE SOLD</t>
         </is>
       </c>
-      <c r="B38" s="37">
+      <c r="B38" s="38">
         <f>B34/B18</f>
         <v/>
       </c>
@@ -8264,27 +8265,27 @@
           <t>Clinker produced (Mt)</t>
         </is>
       </c>
-      <c r="B46" s="34">
+      <c r="B46" s="35">
         <f>$B$5*B45</f>
         <v/>
       </c>
-      <c r="C46" s="34">
+      <c r="C46" s="35">
         <f>$B$5*C45</f>
         <v/>
       </c>
-      <c r="D46" s="34">
+      <c r="D46" s="35">
         <f>$B$5*D45</f>
         <v/>
       </c>
-      <c r="E46" s="34">
+      <c r="E46" s="35">
         <f>$B$5*E45</f>
         <v/>
       </c>
-      <c r="F46" s="34">
+      <c r="F46" s="35">
         <f>$B$5*F45</f>
         <v/>
       </c>
-      <c r="G46" s="34">
+      <c r="G46" s="35">
         <f>$B$5*G45</f>
         <v/>
       </c>
@@ -8326,27 +8327,27 @@
           <t>Clinker exported (Mt)</t>
         </is>
       </c>
-      <c r="B48" s="34">
+      <c r="B48" s="35">
         <f>B46*B47</f>
         <v/>
       </c>
-      <c r="C48" s="34">
+      <c r="C48" s="35">
         <f>C46*C47</f>
         <v/>
       </c>
-      <c r="D48" s="34">
+      <c r="D48" s="35">
         <f>D46*D47</f>
         <v/>
       </c>
-      <c r="E48" s="34">
+      <c r="E48" s="35">
         <f>E46*E47</f>
         <v/>
       </c>
-      <c r="F48" s="34">
+      <c r="F48" s="35">
         <f>F46*F47</f>
         <v/>
       </c>
-      <c r="G48" s="34">
+      <c r="G48" s="35">
         <f>G46*G47</f>
         <v/>
       </c>
@@ -8357,27 +8358,27 @@
           <t>Clinker ground (Mt)</t>
         </is>
       </c>
-      <c r="B49" s="34">
+      <c r="B49" s="35">
         <f>B46-B48</f>
         <v/>
       </c>
-      <c r="C49" s="34">
+      <c r="C49" s="35">
         <f>C46-C48</f>
         <v/>
       </c>
-      <c r="D49" s="34">
+      <c r="D49" s="35">
         <f>D46-D48</f>
         <v/>
       </c>
-      <c r="E49" s="34">
+      <c r="E49" s="35">
         <f>E46-E48</f>
         <v/>
       </c>
-      <c r="F49" s="34">
+      <c r="F49" s="35">
         <f>F46-F48</f>
         <v/>
       </c>
-      <c r="G49" s="34">
+      <c r="G49" s="35">
         <f>G46-G48</f>
         <v/>
       </c>
@@ -8388,27 +8389,27 @@
           <t>Cement produced (Mt)</t>
         </is>
       </c>
-      <c r="B50" s="34">
+      <c r="B50" s="35">
         <f>B49/$B$11</f>
         <v/>
       </c>
-      <c r="C50" s="34">
+      <c r="C50" s="35">
         <f>C49/$B$11</f>
         <v/>
       </c>
-      <c r="D50" s="34">
+      <c r="D50" s="35">
         <f>D49/$B$11</f>
         <v/>
       </c>
-      <c r="E50" s="34">
+      <c r="E50" s="35">
         <f>E49/$B$11</f>
         <v/>
       </c>
-      <c r="F50" s="34">
+      <c r="F50" s="35">
         <f>F49/$B$11</f>
         <v/>
       </c>
-      <c r="G50" s="34">
+      <c r="G50" s="35">
         <f>G49/$B$11</f>
         <v/>
       </c>
@@ -8481,27 +8482,27 @@
           <t>Cement exported (Mt)</t>
         </is>
       </c>
-      <c r="B53" s="34">
+      <c r="B53" s="35">
         <f>B75*B52</f>
         <v/>
       </c>
-      <c r="C53" s="34">
+      <c r="C53" s="35">
         <f>C75*C52</f>
         <v/>
       </c>
-      <c r="D53" s="34">
+      <c r="D53" s="35">
         <f>D75*D52</f>
         <v/>
       </c>
-      <c r="E53" s="34">
+      <c r="E53" s="35">
         <f>E75*E52</f>
         <v/>
       </c>
-      <c r="F53" s="34">
+      <c r="F53" s="35">
         <f>F75*F52</f>
         <v/>
       </c>
-      <c r="G53" s="34">
+      <c r="G53" s="35">
         <f>G75*G52</f>
         <v/>
       </c>
@@ -8512,27 +8513,27 @@
           <t>Cement local (Mt)</t>
         </is>
       </c>
-      <c r="B54" s="34">
+      <c r="B54" s="35">
         <f>B75-B53</f>
         <v/>
       </c>
-      <c r="C54" s="34">
+      <c r="C54" s="35">
         <f>C75-C53</f>
         <v/>
       </c>
-      <c r="D54" s="34">
+      <c r="D54" s="35">
         <f>D75-D53</f>
         <v/>
       </c>
-      <c r="E54" s="34">
+      <c r="E54" s="35">
         <f>E75-E53</f>
         <v/>
       </c>
-      <c r="F54" s="34">
+      <c r="F54" s="35">
         <f>F75-F53</f>
         <v/>
       </c>
-      <c r="G54" s="34">
+      <c r="G54" s="35">
         <f>G75-G53</f>
         <v/>
       </c>
@@ -8543,27 +8544,27 @@
           <t>TOTAL DESPATCHES (Mt)</t>
         </is>
       </c>
-      <c r="B55" s="36">
+      <c r="B55" s="37">
         <f>B75+B48</f>
         <v/>
       </c>
-      <c r="C55" s="36">
+      <c r="C55" s="37">
         <f>C75+C48</f>
         <v/>
       </c>
-      <c r="D55" s="36">
+      <c r="D55" s="37">
         <f>D75+D48</f>
         <v/>
       </c>
-      <c r="E55" s="36">
+      <c r="E55" s="37">
         <f>E75+E48</f>
         <v/>
       </c>
-      <c r="F55" s="36">
+      <c r="F55" s="37">
         <f>F75+F48</f>
         <v/>
       </c>
-      <c r="G55" s="36">
+      <c r="G55" s="37">
         <f>G75+G48</f>
         <v/>
       </c>
@@ -8791,27 +8792,27 @@
           <t>REVENUE (EGP mn)</t>
         </is>
       </c>
-      <c r="B63" s="37">
+      <c r="B63" s="38">
         <f>B62*(1+Assumptions!$B$20)</f>
         <v/>
       </c>
-      <c r="C63" s="37">
+      <c r="C63" s="38">
         <f>C62*(1+Assumptions!$B$148)</f>
         <v/>
       </c>
-      <c r="D63" s="37">
+      <c r="D63" s="38">
         <f>D62*(1+Assumptions!$B$148)</f>
         <v/>
       </c>
-      <c r="E63" s="37">
+      <c r="E63" s="38">
         <f>E62*(1+Assumptions!$B$148)</f>
         <v/>
       </c>
-      <c r="F63" s="37">
+      <c r="F63" s="38">
         <f>F62*(1+Assumptions!$B$148)</f>
         <v/>
       </c>
-      <c r="G63" s="37">
+      <c r="G63" s="38">
         <f>G62*(1+Assumptions!$B$148)</f>
         <v/>
       </c>
@@ -9039,27 +9040,27 @@
           <t>EBITDA  (AN OUTPUT)</t>
         </is>
       </c>
-      <c r="B71" s="37">
+      <c r="B71" s="38">
         <f>B63-B68-B70</f>
         <v/>
       </c>
-      <c r="C71" s="37">
+      <c r="C71" s="38">
         <f>C63-C68-C70</f>
         <v/>
       </c>
-      <c r="D71" s="37">
+      <c r="D71" s="38">
         <f>D63-D68-D70</f>
         <v/>
       </c>
-      <c r="E71" s="37">
+      <c r="E71" s="38">
         <f>E63-E68-E70</f>
         <v/>
       </c>
-      <c r="F71" s="37">
+      <c r="F71" s="38">
         <f>F63-F68-F70</f>
         <v/>
       </c>
-      <c r="G71" s="37">
+      <c r="G71" s="38">
         <f>G63-G68-G70</f>
         <v/>
       </c>
@@ -9132,27 +9133,27 @@
           <t>Draw from finished-goods stock (Mt)  (DRIVER)</t>
         </is>
       </c>
-      <c r="B74" s="35">
+      <c r="B74" s="36">
         <f>Assumptions!$B$26</f>
         <v/>
       </c>
-      <c r="C74" s="35">
+      <c r="C74" s="36">
         <f>Assumptions!$C$26</f>
         <v/>
       </c>
-      <c r="D74" s="35">
+      <c r="D74" s="36">
         <f>Assumptions!$D$26</f>
         <v/>
       </c>
-      <c r="E74" s="35">
+      <c r="E74" s="36">
         <f>Assumptions!$E$26</f>
         <v/>
       </c>
-      <c r="F74" s="35">
+      <c r="F74" s="36">
         <f>Assumptions!$F$26</f>
         <v/>
       </c>
-      <c r="G74" s="35">
+      <c r="G74" s="36">
         <f>Assumptions!$G$26</f>
         <v/>
       </c>
@@ -9163,27 +9164,27 @@
           <t>VALIDATION — AND A PRICE TEST THAT CAN ACTUALLY FAIL</t>
         </is>
       </c>
-      <c r="B75" s="39">
+      <c r="B75" s="40">
         <f>B50+B74</f>
         <v/>
       </c>
-      <c r="C75" s="39">
+      <c r="C75" s="40">
         <f>C50+C74</f>
         <v/>
       </c>
-      <c r="D75" s="39">
+      <c r="D75" s="40">
         <f>D50+D74</f>
         <v/>
       </c>
-      <c r="E75" s="39">
+      <c r="E75" s="40">
         <f>E50+E74</f>
         <v/>
       </c>
-      <c r="F75" s="39">
+      <c r="F75" s="40">
         <f>F50+F74</f>
         <v/>
       </c>
-      <c r="G75" s="39">
+      <c r="G75" s="40">
         <f>G50+G74</f>
         <v/>
       </c>
@@ -9328,7 +9329,7 @@
           <t>Kiln clinker capacity (Mt, audited note 1)</t>
         </is>
       </c>
-      <c r="B92" s="33">
+      <c r="B92" s="34">
         <f>Assumptions!$B$15</f>
         <v/>
       </c>
@@ -9339,7 +9340,7 @@
           <t>Peak clinker required across the forecast (Mt)</t>
         </is>
       </c>
-      <c r="B93" s="34">
+      <c r="B93" s="35">
         <f>MAX(C46:G46)</f>
         <v/>
       </c>
@@ -9361,7 +9362,7 @@
           <t>Headroom at the kiln (Mt of clinker)</t>
         </is>
       </c>
-      <c r="B95" s="34">
+      <c r="B95" s="35">
         <f>B92-B93</f>
         <v/>
       </c>
@@ -9372,7 +9373,7 @@
           <t>Cement mill capacity (Mt, audited note 1)</t>
         </is>
       </c>
-      <c r="B96" s="33">
+      <c r="B96" s="34">
         <f>Assumptions!$B$14</f>
         <v/>
       </c>
@@ -9383,7 +9384,7 @@
           <t>Peak cement produced across the forecast (Mt)</t>
         </is>
       </c>
-      <c r="B97" s="34">
+      <c r="B97" s="35">
         <f>MAX(C50:G50)</f>
         <v/>
       </c>
@@ -9405,7 +9406,7 @@
           <t>Headroom at the mill (Mt of cement)</t>
         </is>
       </c>
-      <c r="B99" s="34">
+      <c r="B99" s="35">
         <f>B96-B97</f>
         <v/>
       </c>
@@ -9560,7 +9561,7 @@
           <t>Normalised EBITDA</t>
         </is>
       </c>
-      <c r="B9" s="37">
+      <c r="B9" s="38">
         <f>B7*B8</f>
         <v/>
       </c>
@@ -9593,7 +9594,7 @@
           <t>Normalised NOPAT</t>
         </is>
       </c>
-      <c r="B12" s="37">
+      <c r="B12" s="38">
         <f>B11*(1-Assumptions!$B$9)</f>
         <v/>
       </c>
@@ -9650,7 +9651,7 @@
           <t>Justified EV/EBITDA</t>
         </is>
       </c>
-      <c r="B18" s="40">
+      <c r="B18" s="41">
         <f>Assumptions!$B$157</f>
         <v/>
       </c>
@@ -9729,7 +9730,7 @@
           <t>Justified price / earnings</t>
         </is>
       </c>
-      <c r="B26" s="40">
+      <c r="B26" s="41">
         <f>Assumptions!$B$158</f>
         <v/>
       </c>
@@ -10148,23 +10149,23 @@
           <t>FREE CASH FLOW TO THE FIRM</t>
         </is>
       </c>
-      <c r="B15" s="37">
+      <c r="B15" s="38">
         <f>(B11+B12+B13+B14)*(1-Assumptions!$B$54)</f>
         <v/>
       </c>
-      <c r="C15" s="37">
+      <c r="C15" s="38">
         <f>C11+C12+C13+C14</f>
         <v/>
       </c>
-      <c r="D15" s="37">
+      <c r="D15" s="38">
         <f>D11+D12+D13+D14</f>
         <v/>
       </c>
-      <c r="E15" s="37">
+      <c r="E15" s="38">
         <f>E11+E12+E13+E14</f>
         <v/>
       </c>
-      <c r="F15" s="37">
+      <c r="F15" s="38">
         <f>F11+F12+F13+F14</f>
         <v/>
       </c>
@@ -10175,23 +10176,23 @@
           <t>Glide fraction</t>
         </is>
       </c>
-      <c r="B16" s="41">
+      <c r="B16" s="42">
         <f>(Assumptions!$B$35-Assumptions!$B$35)/(Assumptions!$B$35-Assumptions!$F$35)</f>
         <v/>
       </c>
-      <c r="C16" s="41">
+      <c r="C16" s="42">
         <f>(Assumptions!$B$35-Assumptions!$C$35)/(Assumptions!$B$35-Assumptions!$F$35)</f>
         <v/>
       </c>
-      <c r="D16" s="41">
+      <c r="D16" s="42">
         <f>(Assumptions!$B$35-Assumptions!$D$35)/(Assumptions!$B$35-Assumptions!$F$35)</f>
         <v/>
       </c>
-      <c r="E16" s="41">
+      <c r="E16" s="42">
         <f>(Assumptions!$B$35-Assumptions!$E$35)/(Assumptions!$B$35-Assumptions!$F$35)</f>
         <v/>
       </c>
-      <c r="F16" s="41">
+      <c r="F16" s="42">
         <f>(Assumptions!$B$35-Assumptions!$F$35)/(Assumptions!$B$35-Assumptions!$F$35)</f>
         <v/>
       </c>
@@ -10202,23 +10203,23 @@
           <t>Forward cost of capital</t>
         </is>
       </c>
-      <c r="B17" s="42">
+      <c r="B17" s="30">
         <f>$C$40-($C$40-$C$50)*B16</f>
         <v/>
       </c>
-      <c r="C17" s="42">
+      <c r="C17" s="30">
         <f>$C$40-($C$40-$C$50)*C16</f>
         <v/>
       </c>
-      <c r="D17" s="42">
+      <c r="D17" s="30">
         <f>$C$40-($C$40-$C$50)*D16</f>
         <v/>
       </c>
-      <c r="E17" s="42">
+      <c r="E17" s="30">
         <f>$C$40-($C$40-$C$50)*E16</f>
         <v/>
       </c>
-      <c r="F17" s="42">
+      <c r="F17" s="30">
         <f>$C$40-($C$40-$C$50)*F16</f>
         <v/>
       </c>
@@ -10229,23 +10230,23 @@
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="B18" s="41">
+      <c r="B18" s="42">
         <f>1/(1+B17)^((1-Assumptions!$B$54)/2)</f>
         <v/>
       </c>
-      <c r="C18" s="41">
+      <c r="C18" s="42">
         <f>1/((1+B17)^(1-Assumptions!$B$54)*(1+C17)^0.5)</f>
         <v/>
       </c>
-      <c r="D18" s="41">
+      <c r="D18" s="42">
         <f>1/((1+B17)^(1-Assumptions!$B$54)*(1+C17)*(1+D17)^0.5)</f>
         <v/>
       </c>
-      <c r="E18" s="41">
+      <c r="E18" s="42">
         <f>1/((1+B17)^(1-Assumptions!$B$54)*(1+C17)*(1+D17)*(1+E17)^0.5)</f>
         <v/>
       </c>
-      <c r="F18" s="41">
+      <c r="F18" s="42">
         <f>1/((1+B17)^(1-Assumptions!$B$54)*(1+C17)*(1+D17)*(1+E17)*(1+F17)^0.5)</f>
         <v/>
       </c>
@@ -10428,7 +10429,7 @@
           <t>End-of-window discount factor  (t = 4.50y, not the year-5 mid-point)</t>
         </is>
       </c>
-      <c r="B29" s="41">
+      <c r="B29" s="42">
         <f>1/((1+B17)^(1-Assumptions!$B$54)*(1+C17)*(1+D17)*(1+E17)*(1+F17))</f>
         <v/>
       </c>
@@ -10475,7 +10476,7 @@
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="B33" s="37">
+      <c r="B33" s="38">
         <f>B31+B32</f>
         <v/>
       </c>
@@ -10517,7 +10518,7 @@
         <f>Assumptions!$B$115+B15/(1-Assumptions!$B$54)*Assumptions!$B$54+Assumptions!$B$115*Assumptions!$B$36*Assumptions!$B$54*(1-Assumptions!$B$9)-Assumptions!$B$134</f>
         <v/>
       </c>
-      <c r="C36" s="42">
+      <c r="C36" s="30">
         <f>Assumptions!$B$41</f>
         <v/>
       </c>
@@ -10537,7 +10538,7 @@
         <f>(B36-Assumptions!$B$141-B38-B39)/B43</f>
         <v/>
       </c>
-      <c r="C37" s="42">
+      <c r="C37" s="30">
         <f>-Assumptions!$B$42</f>
         <v/>
       </c>
@@ -10557,7 +10558,7 @@
         <f>Assumptions!$B$142</f>
         <v/>
       </c>
-      <c r="C38" s="42">
+      <c r="C38" s="30">
         <f>C36+C37</f>
         <v/>
       </c>
@@ -10577,7 +10578,7 @@
         <f>-Assumptions!$B$143</f>
         <v/>
       </c>
-      <c r="C39" s="42">
+      <c r="C39" s="30">
         <f>C38+Assumptions!$B$10*Assumptions!$B$44+Assumptions!$B$45</f>
         <v/>
       </c>
@@ -10633,11 +10634,11 @@
           <t>Equity value</t>
         </is>
       </c>
-      <c r="B42" s="37">
+      <c r="B42" s="38">
         <f>B33+B40+B41</f>
         <v/>
       </c>
-      <c r="C42" s="42">
+      <c r="C42" s="30">
         <f>C41*(1-Assumptions!$B$8)</f>
         <v/>
       </c>
@@ -10657,7 +10658,7 @@
         <f>Assumptions!$B$6-Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="C43" s="42">
+      <c r="C43" s="30">
         <f>C44/(C44+C45)</f>
         <v/>
       </c>
@@ -10710,7 +10711,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="C47" s="34">
+      <c r="C47" s="35">
         <f>Assumptions!$B$10/(1+(1-Assumptions!$B$8)*C43/(1-C43))*(1+(1-Assumptions!$B$8)*Assumptions!$B$52/(1-Assumptions!$B$52))</f>
         <v/>
       </c>
@@ -10721,7 +10722,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="C48" s="42">
+      <c r="C48" s="30">
         <f>Assumptions!$B$50+C47*Assumptions!$B$51</f>
         <v/>
       </c>
@@ -10732,7 +10733,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="C49" s="42">
+      <c r="C49" s="30">
         <f>Assumptions!$B$49*(1-Assumptions!$B$8)</f>
         <v/>
       </c>
@@ -10754,7 +10755,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="C51" s="42">
+      <c r="C51" s="30">
         <f>Assumptions!$B$41+Assumptions!$B$10*Assumptions!$B$43</f>
         <v/>
       </c>
@@ -10806,7 +10807,7 @@
           <t>CIB facility rate — EGP corridor + 0.6%</t>
         </is>
       </c>
-      <c r="B56" s="42">
+      <c r="B56" s="30">
         <f>Assumptions!$B$47</f>
         <v/>
       </c>
@@ -10817,7 +10818,7 @@
           <t>NBE/KfW facility rate — Euribor + 3.00%</t>
         </is>
       </c>
-      <c r="B57" s="42">
+      <c r="B57" s="30">
         <f>Assumptions!$B$46+0.03</f>
         <v/>
       </c>
@@ -10828,7 +10829,7 @@
           <t>EBRD facility rate — Euribor + 4.35%</t>
         </is>
       </c>
-      <c r="B58" s="42">
+      <c r="B58" s="30">
         <f>Assumptions!$B$46+0.0435</f>
         <v/>
       </c>
@@ -10850,7 +10851,7 @@
           <t>Effective rate computed FY2024 (interest / average debt)</t>
         </is>
       </c>
-      <c r="B60" s="42">
+      <c r="B60" s="30">
         <f>(Assumptions!$B$131+Assumptions!$B$132)/((Assumptions!$B$128+Assumptions!$B$127)/2)</f>
         <v/>
       </c>
@@ -10861,7 +10862,7 @@
           <t>Effective rate computed FY2025</t>
         </is>
       </c>
-      <c r="B61" s="42">
+      <c r="B61" s="30">
         <f>(Assumptions!$B$129+Assumptions!$B$130)/((Assumptions!$B$127+C44-Assumptions!$B$126)/2)</f>
         <v/>
       </c>
@@ -10872,7 +10873,7 @@
           <t>Effective rate computed Q1-2026, annualised</t>
         </is>
       </c>
-      <c r="B62" s="42">
+      <c r="B62" s="30">
         <f>Assumptions!$B$153*4/((C44+Assumptions!$B$141)/2)</f>
         <v/>
       </c>
@@ -11175,35 +11176,35 @@
           <t>OPERATING PROFIT</t>
         </is>
       </c>
-      <c r="B11" s="37">
+      <c r="B11" s="38">
         <f>B7+B9+B10</f>
         <v/>
       </c>
-      <c r="C11" s="37">
+      <c r="C11" s="38">
         <f>C7+C9+C10</f>
         <v/>
       </c>
-      <c r="D11" s="37">
+      <c r="D11" s="38">
         <f>D7+D9+D10</f>
         <v/>
       </c>
-      <c r="E11" s="37">
+      <c r="E11" s="38">
         <f>E14-E13+Assumptions!$B$150*'Segments'!C60+Assumptions!$B$150*'Segments'!C61+Assumptions!$B$151*Assumptions!$C$30</f>
         <v/>
       </c>
-      <c r="F11" s="37">
+      <c r="F11" s="38">
         <f>F14-F13+Assumptions!$B$150*'Segments'!D60+Assumptions!$B$150*'Segments'!D61+Assumptions!$B$151*Assumptions!$D$30</f>
         <v/>
       </c>
-      <c r="G11" s="37">
+      <c r="G11" s="38">
         <f>G14-G13+Assumptions!$B$150*'Segments'!E60+Assumptions!$B$150*'Segments'!E61+Assumptions!$B$151*Assumptions!$E$30</f>
         <v/>
       </c>
-      <c r="H11" s="37">
+      <c r="H11" s="38">
         <f>H14-H13+Assumptions!$B$150*'Segments'!F60+Assumptions!$B$150*'Segments'!F61+Assumptions!$B$151*Assumptions!$F$30</f>
         <v/>
       </c>
-      <c r="I11" s="37">
+      <c r="I11" s="38">
         <f>I14-I13+Assumptions!$B$150*'Segments'!G60+Assumptions!$B$150*'Segments'!G61+Assumptions!$B$151*Assumptions!$G$30</f>
         <v/>
       </c>
@@ -11292,35 +11293,35 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B14" s="37">
+      <c r="B14" s="38">
         <f>B12+B13</f>
         <v/>
       </c>
-      <c r="C14" s="37">
+      <c r="C14" s="38">
         <f>C12+C13</f>
         <v/>
       </c>
-      <c r="D14" s="37">
+      <c r="D14" s="38">
         <f>D12+D13</f>
         <v/>
       </c>
-      <c r="E14" s="32">
+      <c r="E14" s="33">
         <f>DCF!B7</f>
         <v/>
       </c>
-      <c r="F14" s="32">
+      <c r="F14" s="33">
         <f>DCF!C7</f>
         <v/>
       </c>
-      <c r="G14" s="32">
+      <c r="G14" s="33">
         <f>DCF!D7</f>
         <v/>
       </c>
-      <c r="H14" s="32">
+      <c r="H14" s="33">
         <f>DCF!E7</f>
         <v/>
       </c>
-      <c r="I14" s="32">
+      <c r="I14" s="33">
         <f>DCF!F7</f>
         <v/>
       </c>
@@ -11526,35 +11527,35 @@
           <t>Attributable profit</t>
         </is>
       </c>
-      <c r="B20" s="32">
+      <c r="B20" s="33">
         <f>Assumptions!$B$77</f>
         <v/>
       </c>
-      <c r="C20" s="32">
+      <c r="C20" s="33">
         <f>Assumptions!$B$78</f>
         <v/>
       </c>
-      <c r="D20" s="32">
+      <c r="D20" s="33">
         <f>Assumptions!$B$79</f>
         <v/>
       </c>
-      <c r="E20" s="37">
+      <c r="E20" s="38">
         <f>E17+E18</f>
         <v/>
       </c>
-      <c r="F20" s="37">
+      <c r="F20" s="38">
         <f>F17+F18</f>
         <v/>
       </c>
-      <c r="G20" s="37">
+      <c r="G20" s="38">
         <f>G17+G18</f>
         <v/>
       </c>
-      <c r="H20" s="37">
+      <c r="H20" s="38">
         <f>H17+H18</f>
         <v/>
       </c>
-      <c r="I20" s="37">
+      <c r="I20" s="38">
         <f>I17+I18</f>
         <v/>
       </c>

--- a/engine/publish_queue/ARCC/ARCC_Valuation_Model_10092026_public.xlsx
+++ b/engine/publish_queue/ARCC/ARCC_Valuation_Model_10092026_public.xlsx
@@ -2829,7 +2829,7 @@
         </is>
       </c>
       <c r="B26" s="24" t="n">
-        <v>1</v>
+        <v>0.9375</v>
       </c>
     </row>
     <row r="27">
@@ -2849,7 +2849,7 @@
         </is>
       </c>
       <c r="B28" s="32" t="n">
-        <v>1.234292255993717</v>
+        <v>1.231464898065024</v>
       </c>
     </row>
     <row r="31">
